--- a/Modul Quantitative Methoden I_Termine.xlsx
+++ b/Modul Quantitative Methoden I_Termine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stephangoerigk/Desktop/Universität/CFH/Lehre/Bachelor/Quantitative Methoden I/VO_Statistik I/Statistik_I_Folien/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicosteffen/Documents/01 Arbeit/01 CFH/01 Stephan Goerigk/R/Github Repositories/QMI/QMI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73373BC-1A1F-FE4C-BB7E-611862EBBA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0231261F-FB29-204C-97A7-A878AC529A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="1840" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Einheit</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Schätzungen und Stichprobenfehler</t>
+  </si>
+  <si>
+    <t>Curriculare Reserve</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>45763</v>
+        <v>45762</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -419,7 +422,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>45770</v>
+        <v>45769</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>4</v>
@@ -436,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8">
-        <v>45777</v>
+        <v>45776</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -453,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="8">
-        <v>45784</v>
+        <v>45783</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -470,7 +473,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8">
-        <v>45791</v>
+        <v>45790</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>14</v>
@@ -485,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8">
-        <v>45798</v>
+        <v>45797</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -500,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8">
-        <v>45812</v>
+        <v>45804</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
@@ -515,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8">
-        <v>45819</v>
+        <v>45818</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>13</v>
@@ -530,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8">
-        <v>45826</v>
+        <v>45825</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
@@ -545,7 +548,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8">
-        <v>45833</v>
+        <v>45832</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
@@ -560,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8">
-        <v>45840</v>
+        <v>45839</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>9</v>
@@ -575,7 +578,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8">
-        <v>45847</v>
+        <v>45846</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
@@ -590,12 +593,23 @@
         <v>13</v>
       </c>
       <c r="B14" s="8">
-        <v>45854</v>
+        <v>45853</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46225</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="5"/>
@@ -975,5 +989,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/Modul Quantitative Methoden I_Termine.xlsx
+++ b/Modul Quantitative Methoden I_Termine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicosteffen/Documents/01 Arbeit/01 CFH/01 Stephan Goerigk/R/Github Repositories/QMI/QMI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0231261F-FB29-204C-97A7-A878AC529A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADD0549-4197-FC4E-88C3-FB59639A9054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="1840" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -405,7 +405,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>45762</v>
+        <v>46127</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -422,7 +422,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>45769</v>
+        <v>46134</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>4</v>
@@ -439,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8">
-        <v>45776</v>
+        <v>46141</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="8">
-        <v>45783</v>
+        <v>46148</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -473,7 +473,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8">
-        <v>45790</v>
+        <v>46155</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>14</v>
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8">
-        <v>45797</v>
+        <v>46162</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>15</v>
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8">
-        <v>45804</v>
+        <v>46169</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>7</v>
@@ -518,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8">
-        <v>45818</v>
+        <v>46183</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>13</v>
@@ -533,7 +533,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8">
-        <v>45825</v>
+        <v>46190</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
@@ -548,7 +548,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8">
-        <v>45832</v>
+        <v>46197</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
@@ -563,7 +563,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8">
-        <v>45839</v>
+        <v>46204</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>9</v>
@@ -578,7 +578,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8">
-        <v>45846</v>
+        <v>46211</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
@@ -593,7 +593,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8">
-        <v>45853</v>
+        <v>46218</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>16</v>
